--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104519_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104519_W7.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3369</v>
+        <v>6.9482</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8807</v>
+        <v>4.1395</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4562</v>
+        <v>2.8087</v>
       </c>
       <c r="G2" t="n">
-        <v>0.142</v>
+        <v>0.1419</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3392</v>
+        <v>0.3308</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1972</v>
+        <v>-0.1888</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2509</v>
+        <v>-0.2773</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2882</v>
+        <v>-0.3145</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3929</v>
+        <v>0.4192</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6274</v>
+        <v>0.6452</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4688</v>
+        <v>0.1509</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.744</v>
+        <v>-0.4372</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2752</v>
+        <v>0.5881</v>
       </c>
       <c r="V2" t="n">
-        <v>5.3026</v>
+        <v>5.2896</v>
       </c>
       <c r="W2" t="n">
-        <v>6.0097</v>
+        <v>5.9921</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. TAVARES</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9583</v>
+        <v>3.5286</v>
       </c>
       <c r="E3" t="n">
-        <v>2.071</v>
+        <v>1.4906</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8873</v>
+        <v>2.0381</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7784</v>
+        <v>1.8445</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6955</v>
+        <v>0.0405</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.474</v>
+        <v>1.804</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7504</v>
+        <v>0.5663</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7131</v>
+        <v>-0.6625</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0373</v>
+        <v>1.2288</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5289</v>
+        <v>1.2782</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0176</v>
+        <v>0.703</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5113</v>
+        <v>0.5752</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9488</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9488</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4023</v>
+        <v>0.3183</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5455</v>
+        <v>-0.1652</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8568</v>
+        <v>0.4835</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2249</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6105</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>E. TAVARES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0203</v>
+        <v>3.259</v>
       </c>
       <c r="E4" t="n">
-        <v>1.631</v>
+        <v>0.4221</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3893</v>
+        <v>2.8368</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8482</v>
+        <v>-0.7688</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0463</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8019</v>
+        <v>-1.4638</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5867</v>
+        <v>0.7332</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6447000000000001</v>
+        <v>0.696</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2315</v>
+        <v>0.0372</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2614</v>
+        <v>-1.502</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6909999999999999</v>
+        <v>-0.0009</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5705</v>
+        <v>-1.5011</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>2.9592</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>2.9592</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8111</v>
+        <v>0.6816</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0484</v>
+        <v>-0.0819</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8595</v>
+        <v>0.7634</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>-0.2292</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9356</v>
+        <v>2.706</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0675</v>
+        <v>0.8615</v>
       </c>
       <c r="F5" t="n">
-        <v>3.003</v>
+        <v>1.8445</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2901</v>
+        <v>1.4575</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3923</v>
+        <v>0.9336</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6824</v>
+        <v>0.5239</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3372</v>
+        <v>0.9385</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8943</v>
+        <v>0.403</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2315</v>
+        <v>0.5355</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0471</v>
+        <v>0.519</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5019</v>
+        <v>0.5306</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.549</v>
+        <v>-0.0116</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.722</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9935</v>
+        <v>0.1103</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3217</v>
+        <v>-0.077</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3281</v>
+        <v>0.1873</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5364</v>
+        <v>2.5049</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0035</v>
+        <v>-0.6856</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5399</v>
+        <v>3.1905</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4696</v>
+        <v>0.2853</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9365</v>
+        <v>-0.4016</v>
       </c>
       <c r="I6" t="n">
-        <v>0.533</v>
+        <v>0.6869</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.311</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4187</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5516</v>
+        <v>1.2288</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4992</v>
+        <v>-0.0257</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5178</v>
+        <v>0.5162</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0186</v>
+        <v>-0.5419</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>2.7316</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0673</v>
+        <v>-0.4147</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9739</v>
+        <v>-0.8993</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0935</v>
+        <v>0.4846</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8398</v>
+        <v>0.7481</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7532</v>
+        <v>-0.4978</v>
       </c>
       <c r="F7" t="n">
-        <v>1.593</v>
+        <v>1.2459</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.1832</v>
+        <v>-3.1938</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0607</v>
+        <v>0.0522</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.244</v>
+        <v>-3.246</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.9448</v>
+        <v>-1.9772</v>
       </c>
       <c r="K7" t="n">
-        <v>0.377</v>
+        <v>0.3545</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.3218</v>
+        <v>-2.3317</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2384</v>
+        <v>-1.2166</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.1672</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.113</v>
+        <v>-0.8087</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0168</v>
+        <v>0.6415</v>
       </c>
       <c r="V7" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="W7" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4084</v>
+        <v>0.3338</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1015</v>
+        <v>-1.4575</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5098</v>
+        <v>1.7913</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8351</v>
+        <v>-1.3524</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0258</v>
+        <v>2.0964</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.861</v>
+        <v>-3.4488</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5662</v>
+        <v>-1.0529</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6651</v>
+        <v>2.0684</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.901</v>
+        <v>-3.1213</v>
       </c>
       <c r="M8" t="n">
-        <v>0.731</v>
+        <v>-0.2995</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.028</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04</v>
+        <v>-0.3275</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>2.2763</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>2.2763</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9506</v>
+        <v>0.4994</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5989</v>
+        <v>-0.4046</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3517</v>
+        <v>0.9039</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3379</v>
+        <v>0.3087</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7548</v>
+        <v>-1.7718</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0927</v>
+        <v>2.0806</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2325</v>
+        <v>-1.2322</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4602</v>
+        <v>0.4677</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6927</v>
+        <v>-1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1503</v>
+        <v>-1.1629</v>
       </c>
       <c r="K9" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2023</v>
+        <v>-1.2146</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0822</v>
+        <v>-0.0694</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4082</v>
+        <v>0.416</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.405</v>
+        <v>-0.4378</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7652</v>
+        <v>-0.7667</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3602</v>
+        <v>0.3289</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1401</v>
+        <v>-0.3131</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2126</v>
+        <v>-2.7537</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0725</v>
+        <v>2.4406</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.349</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0922</v>
+        <v>0.034</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.4413</v>
+        <v>-0.8641</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0301</v>
+        <v>-1.578</v>
       </c>
       <c r="K10" t="n">
-        <v>2.078</v>
+        <v>-0.669</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.1081</v>
+        <v>-0.909</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3189</v>
+        <v>0.7479</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0142</v>
+        <v>0.703</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3331</v>
+        <v>0.0449</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0333</v>
+        <v>0.2195</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1825</v>
+        <v>-0.0375</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2158</v>
+        <v>0.257</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9143</v>
+        <v>-1.2261</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4423</v>
+        <v>-1.7331</v>
       </c>
       <c r="F11" t="n">
-        <v>0.528</v>
+        <v>0.5069</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6848</v>
+        <v>-0.6791</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3015</v>
+        <v>0.307</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9862</v>
+        <v>-0.9861</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6771</v>
+        <v>-0.6807</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0077</v>
+        <v>0.0016</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2669</v>
+        <v>0.2725</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2241</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.369</v>
+        <v>0.0858</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1449</v>
+        <v>-0.1775</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5877</v>
+        <v>-2.3623</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.508</v>
+        <v>-3.8869</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9203</v>
+        <v>1.5246</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6186</v>
+        <v>-3.6211</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2568</v>
+        <v>1.2606</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.8753</v>
+        <v>-4.8818</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6201</v>
+        <v>-2.6494</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2743</v>
+        <v>1.2615</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.8945</v>
+        <v>-3.911</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9984</v>
+        <v>-0.9717</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0176</v>
+        <v>-0.0009</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.557</v>
+        <v>-0.3346</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4608</v>
+        <v>-0.8018</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.4672</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.7315</v>
+        <v>16.4358</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.260699999999998</v>
+        <v>-5.8727</v>
       </c>
       <c r="F13" t="n">
-        <v>21.992</v>
+        <v>22.3085</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.931699999999999</v>
+        <v>-7.9483</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8224</v>
+        <v>5.8163</v>
       </c>
       <c r="I13" t="n">
-        <v>-13.7544</v>
+        <v>-13.7646</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.5949</v>
+        <v>-6.8294</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4554</v>
+        <v>2.3058</v>
       </c>
       <c r="L13" t="n">
-        <v>-9.0502</v>
+        <v>-9.135300000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3371</v>
+        <v>-1.119</v>
       </c>
       <c r="N13" t="n">
-        <v>3.367</v>
+        <v>3.5104</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.7039</v>
+        <v>-4.629499999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.939299999999999</v>
+        <v>-7.967300000000002</v>
       </c>
       <c r="R13" t="n">
-        <v>21.5492</v>
+        <v>21.6251</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1663999999999999</v>
+        <v>0.5338999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.096100000000001</v>
+        <v>-4.3941</v>
       </c>
       <c r="U13" t="n">
-        <v>4.929500000000001</v>
+        <v>4.927899999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>10.2195</v>
+        <v>10.1922</v>
       </c>
       <c r="W13" t="n">
-        <v>13.3693</v>
+        <v>13.3178</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.1498</v>
+        <v>-3.1256</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4453</v>
+        <v>2.0446</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2708</v>
+        <v>-0.0507</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7161</v>
+        <v>2.0952</v>
       </c>
       <c r="G14" t="n">
-        <v>2.446</v>
+        <v>2.4601</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1585</v>
+        <v>1.1684</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2875</v>
+        <v>1.2917</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8935999999999999</v>
+        <v>0.8789</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3739</v>
+        <v>0.3652</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5524</v>
+        <v>1.5812</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7847</v>
+        <v>0.8032</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.201</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1644</v>
+        <v>-0.9295</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0366</v>
+        <v>0.306</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.258</v>
+        <v>1.4415</v>
       </c>
       <c r="E15" t="n">
-        <v>0.529</v>
+        <v>0.1467</v>
       </c>
       <c r="F15" t="n">
-        <v>0.729</v>
+        <v>1.2947</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6805</v>
+        <v>2.6861</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0576</v>
+        <v>0.0629</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6229</v>
+        <v>2.6232</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0131</v>
+        <v>1.996</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3739</v>
+        <v>0.3652</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6674</v>
+        <v>0.6901</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5132</v>
+        <v>-0.3357</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3085</v>
+        <v>-0.6624</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2048</v>
+        <v>0.3267</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0191</v>
+        <v>0.9692</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0675</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9516</v>
+        <v>1.0572</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5749</v>
+        <v>1.5687</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.339</v>
+        <v>-0.3471</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9139</v>
+        <v>1.9157</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5847</v>
+        <v>0.5466</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3055</v>
+        <v>-0.3317</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8902</v>
+        <v>0.8783</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9902</v>
+        <v>1.022</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0335</v>
+        <v>-0.0154</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0237</v>
+        <v>1.0374</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2686</v>
+        <v>0.2137</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2903</v>
+        <v>-0.407</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5589</v>
+        <v>0.6207</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0828</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.7586</v>
+        <v>-2.4622</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8415</v>
+        <v>2.3709</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1647</v>
+        <v>1.1605</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.9247</v>
+        <v>-1.9352</v>
       </c>
       <c r="I17" t="n">
-        <v>3.0894</v>
+        <v>3.0957</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3877</v>
+        <v>0.3557</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.4035</v>
+        <v>-1.4316</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7912</v>
+        <v>1.7874</v>
       </c>
       <c r="M17" t="n">
-        <v>0.777</v>
+        <v>0.8048</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2982</v>
+        <v>1.3083</v>
       </c>
       <c r="P17" t="n">
-        <v>-4.083</v>
+        <v>-4.0974</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6551</v>
+        <v>0.5089</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7289</v>
+        <v>-0.3743</v>
       </c>
       <c r="U17" t="n">
-        <v>1.384</v>
+        <v>0.8832</v>
       </c>
       <c r="V17" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>A. FONT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.2561</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5434</v>
+        <v>0.2722</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4594</v>
+        <v>-0.5284</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0465</v>
+        <v>1.1538</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4849</v>
+        <v>-0.2073</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5617</v>
+        <v>1.3611</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5845</v>
+        <v>0.7811</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2038</v>
+        <v>0.0517</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3807</v>
+        <v>0.7294</v>
       </c>
       <c r="M18" t="n">
-        <v>1.462</v>
+        <v>0.3727</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2811</v>
+        <v>-0.259</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1809</v>
+        <v>0.6317</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.6293</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3873</v>
+        <v>-0.3205</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5656</v>
+        <v>-0.5089</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8217</v>
+        <v>0.1884</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.2495</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2348</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1033</v>
+        <v>-0.2575</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3382</v>
+        <v>-0.484</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.8068</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6103</v>
+        <v>0.6117</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1946</v>
+        <v>0.1952</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8685</v>
+        <v>0.8646</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8312</v>
+        <v>0.8274</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9603</v>
+        <v>0.4517</v>
       </c>
       <c r="T19" t="n">
-        <v>0.369</v>
+        <v>0.0161</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5913</v>
+        <v>0.4356</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. FONT</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3137</v>
+        <v>-0.9489</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1668</v>
+        <v>-0.7421</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4805</v>
+        <v>-0.2068</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1534</v>
+        <v>-0.4763</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2166</v>
+        <v>-0.8474</v>
       </c>
       <c r="I20" t="n">
-        <v>1.37</v>
+        <v>0.3711</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7929</v>
+        <v>-0.261</v>
       </c>
       <c r="K20" t="n">
-        <v>0.052</v>
+        <v>0.4169</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7409</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3605</v>
+        <v>-0.2154</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2685</v>
+        <v>-1.2643</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6291</v>
+        <v>1.049</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3744</v>
+        <v>0.3194</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6261</v>
+        <v>-0.2535</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2516</v>
+        <v>0.5729</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2234</v>
+        <v>-1.1282</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0833</v>
+        <v>-2.412</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1401</v>
+        <v>1.2838</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4821</v>
+        <v>3.0557</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8499</v>
+        <v>0.4826</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3679</v>
+        <v>2.5731</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2486</v>
+        <v>1.5599</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4258</v>
+        <v>0.1821</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6744</v>
+        <v>1.3778</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2335</v>
+        <v>1.4958</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2758</v>
+        <v>0.3005</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0423</v>
+        <v>1.1953</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-3.6421</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0584</v>
+        <v>0.3428</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6079</v>
+        <v>-0.2583</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6663</v>
+        <v>0.6011</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2534</v>
+        <v>-2.2504</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2534</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4526</v>
+        <v>-3.0988</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2273</v>
+        <v>-1.9026</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2253</v>
+        <v>-1.1962</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7014</v>
+        <v>-0.6955</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6264</v>
+        <v>-1.6175</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1957</v>
+        <v>-1.2133</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4515</v>
+        <v>-1.4586</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4943</v>
+        <v>0.5178</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7531</v>
+        <v>-0.4016</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7652</v>
+        <v>-0.4114</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0121</v>
+        <v>0.0097</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9812</v>
+        <v>-3.9813</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3852</v>
+        <v>-3.3972</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.596</v>
+        <v>-0.5841</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8485</v>
+        <v>-0.8446</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3203</v>
+        <v>-1.3184</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1905</v>
+        <v>0.1906</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.2471</v>
+        <v>-9.947800000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.4975</v>
+        <v>-10.3257</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2505</v>
+        <v>0.3779</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.9072</v>
+        <v>-2.927</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8569</v>
+        <v>-1.8691</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0503</v>
+        <v>-1.058</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.5746</v>
+        <v>-3.6172</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.6979</v>
+        <v>-1.7247</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.8767</v>
+        <v>-1.8925</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6674</v>
+        <v>0.6901</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.9903</v>
+        <v>-5.0079</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.8976</v>
+        <v>-5.9184</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1642</v>
+        <v>0.1661</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0253</v>
+        <v>-0.7901</v>
       </c>
       <c r="U24" t="n">
-        <v>0.861</v>
+        <v>0.9562</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.7316</v>
+        <v>-15.7385</v>
       </c>
       <c r="E25" t="n">
-        <v>-20.8995</v>
+        <v>-21.2191</v>
       </c>
       <c r="F25" t="n">
-        <v>5.167999999999999</v>
+        <v>5.4802</v>
       </c>
       <c r="G25" t="n">
-        <v>7.931700000000001</v>
+        <v>7.9483</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.8225</v>
+        <v>-5.8164</v>
       </c>
       <c r="I25" t="n">
-        <v>13.7543</v>
+        <v>13.7645</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3371</v>
+        <v>1.1189</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.3668</v>
+        <v>-3.5105</v>
       </c>
       <c r="L25" t="n">
-        <v>4.703899999999999</v>
+        <v>4.6294</v>
       </c>
       <c r="M25" t="n">
-        <v>6.594599999999999</v>
+        <v>6.829100000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.4555</v>
+        <v>-2.3058</v>
       </c>
       <c r="O25" t="n">
-        <v>9.0503</v>
+        <v>9.135</v>
       </c>
       <c r="P25" t="n">
-        <v>-13.6099</v>
+        <v>-13.6579</v>
       </c>
       <c r="Q25" t="n">
-        <v>-21.549</v>
+        <v>-21.625</v>
       </c>
       <c r="R25" t="n">
-        <v>7.939100000000001</v>
+        <v>7.9671</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1665000000000001</v>
+        <v>0.1633999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.9298</v>
+        <v>-4.9278</v>
       </c>
       <c r="U25" t="n">
-        <v>5.095999999999999</v>
+        <v>5.0911</v>
       </c>
       <c r="V25" t="n">
-        <v>-10.2197</v>
+        <v>-10.1922</v>
       </c>
       <c r="W25" t="n">
-        <v>4.2424</v>
+        <v>4.2151</v>
       </c>
       <c r="X25" t="n">
-        <v>-14.462</v>
+        <v>-14.4071</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104519_W7.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104519_W7.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-3.1256</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104519_W7.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-14.4071</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
